--- a/data/trans_bre/IP04F-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,56</t>
+          <t>-4,64; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,81</t>
+          <t>-4,16; 5,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 89,4</t>
+          <t>-57,98; 119,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 169,74</t>
+          <t>-49,14; 157,84</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 7,06</t>
+          <t>-1,12; 6,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 8,43</t>
+          <t>0,25; 9,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 128,79</t>
+          <t>-13,85; 120,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 164,52</t>
+          <t>-2,32; 167,94</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 7,08</t>
+          <t>-5,75; 5,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,63</t>
+          <t>-6,45; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 83,74</t>
+          <t>-38,31; 65,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 50,22</t>
+          <t>-63,92; 37,63</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 7,79</t>
+          <t>-4,23; 7,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 6,84</t>
+          <t>-4,53; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 89,81</t>
+          <t>-31,0; 83,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 84,43</t>
+          <t>-35,16; 85,95</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,97</t>
+          <t>-1,18; 3,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,64</t>
+          <t>-1,23; 3,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 52,9</t>
+          <t>-11,65; 49,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 54,23</t>
+          <t>-15,12; 51,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,42</t>
+          <t>-5,03; 4,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,63</t>
+          <t>-4,03; 5,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 119,07</t>
+          <t>-60,4; 108,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 157,84</t>
+          <t>-48,74; 152,04</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,97</t>
+          <t>-1,02; 7,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 9,04</t>
+          <t>-0,46; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 120,3</t>
+          <t>-11,59; 132,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 167,94</t>
+          <t>-5,48; 167,79</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 5,95</t>
+          <t>-5,97; 6,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 2,1</t>
+          <t>-6,39; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 65,24</t>
+          <t>-41,22; 70,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 37,63</t>
+          <t>-61,24; 42,26</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 7,28</t>
+          <t>-4,17; 7,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 6,35</t>
+          <t>-4,71; 7,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 83,36</t>
+          <t>-29,92; 87,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 85,95</t>
+          <t>-36,83; 98,71</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,94</t>
+          <t>-1,0; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,48</t>
+          <t>-1,13; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 49,63</t>
+          <t>-9,96; 52,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 51,07</t>
+          <t>-13,71; 50,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,1</t>
+          <t>-5,16; 3,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 5,42</t>
+          <t>-3,72; 5,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 108,11</t>
+          <t>-58,68; 89,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 152,04</t>
+          <t>-47,62; 169,74</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 7,38</t>
+          <t>-1,19; 7,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 8,2</t>
+          <t>-0,31; 8,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 132,9</t>
+          <t>-16,5; 128,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 167,79</t>
+          <t>-6,89; 164,52</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 6,36</t>
+          <t>-5,38; 7,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,22</t>
+          <t>-6,14; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 70,19</t>
+          <t>-38,02; 83,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 42,26</t>
+          <t>-60,49; 50,22</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 7,27</t>
+          <t>-3,33; 7,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 7,26</t>
+          <t>-4,46; 6,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 87,16</t>
+          <t>-24,73; 89,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 98,71</t>
+          <t>-34,68; 84,43</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,02</t>
+          <t>-1,08; 3,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,37</t>
+          <t>-1,27; 3,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 52,58</t>
+          <t>-10,63; 52,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 50,74</t>
+          <t>-14,68; 54,23</t>
         </is>
       </c>
     </row>
